--- a/data/trans_orig/IP3110_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP3110_2023-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17790</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25138</t>
+          <t>24426</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33114</t>
+          <t>33649</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55142</t>
+          <t>56122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34126</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49630</t>
+          <t>49623</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78548</t>
+          <t>78944</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101619</t>
+          <t>101811</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18978</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32337</t>
+          <t>31040</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>11787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>10838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>19303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>22262</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16032</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32773</t>
+          <t>32518</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59038</t>
+          <t>58539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36455</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60297</t>
+          <t>61016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57446</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109785</t>
+          <t>111207</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33588</t>
+          <t>33606</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88974</t>
+          <t>97733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38397</t>
+          <t>39206</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62059</t>
+          <t>63709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81355</t>
+          <t>81466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157587</t>
+          <t>148015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>58,72%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31983</t>
+          <t>29196</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>40848</t>
+          <t>35437</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11558</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22184</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>20866</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24459</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40138</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29041</t>
+          <t>28666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>29159</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42255</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50343</t>
+          <t>49118</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67703</t>
+          <t>67810</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>13506</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21344</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17305</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12173</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24474</t>
+          <t>24854</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>21426</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41407</t>
+          <t>40369</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30357</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>44537</t>
+          <t>44603</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>21790</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>48254</t>
+          <t>47101</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>56169</t>
+          <t>56864</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>86699</t>
+          <t>87526</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39867</t>
+          <t>42152</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12745</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>53414</t>
+          <t>54525</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,47 +4073,47 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>25,24%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>7982</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>4162</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>13763</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
           <t>5,56%</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>25,13%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>7982</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>4641</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>14196</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25016</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26889</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36949</t>
+          <t>36707</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>49058</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16038</t>
+          <t>16286</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27191</t>
+          <t>26877</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>496</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>499</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>19716</t>
+          <t>19599</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>32720</t>
+          <t>32287</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>32049</t>
+          <t>32083</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>42032</t>
+          <t>41768</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>57773</t>
+          <t>57318</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>17521</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>24160</t>
+          <t>25014</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>31368</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>27798</t>
+          <t>28512</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>48965</t>
+          <t>49537</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>29231</t>
+          <t>29831</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>47869</t>
+          <t>47863</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>45018</t>
+          <t>45455</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>59343</t>
+          <t>58388</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>88579</t>
+          <t>86734</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>40192</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>60109</t>
+          <t>60732</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>55879</t>
+          <t>56412</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>84916</t>
+          <t>84524</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>101214</t>
+          <t>103880</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>135568</t>
+          <t>136060</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>21502</t>
+          <t>21298</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>35146</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>28422</t>
+          <t>27243</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>51932</t>
+          <t>51414</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>817</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>402</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>8640</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>359</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>20486</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>28716</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>24694</t>
+          <t>25027</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>43755</t>
+          <t>45073</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>30522</t>
+          <t>30251</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>19553</t>
+          <t>20053</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>37238</t>
+          <t>37452</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>38990</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>61015</t>
+          <t>61580</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>24966</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>40780</t>
+          <t>42827</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>19350</t>
+          <t>19160</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>35129</t>
+          <t>34573</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>47609</t>
+          <t>47169</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>71585</t>
+          <t>70410</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>41932</t>
+          <t>41411</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>60480</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>54395</t>
+          <t>55012</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>75086</t>
+          <t>75930</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>101049</t>
+          <t>101672</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>131503</t>
+          <t>129823</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>31988</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>51837</t>
+          <t>51529</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>34591</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>59097</t>
+          <t>59053</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>70858</t>
+          <t>71348</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>101199</t>
+          <t>103231</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>100453</t>
+          <t>100603</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>139570</t>
+          <t>139248</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>107056</t>
+          <t>107952</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>146086</t>
+          <t>147416</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>218872</t>
+          <t>219720</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>270935</t>
+          <t>273279</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>227127</t>
+          <t>231260</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>292417</t>
+          <t>293671</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>280156</t>
+          <t>278181</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>333335</t>
+          <t>336364</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>532236</t>
+          <t>531070</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>613258</t>
+          <t>619216</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>113773</t>
+          <t>112716</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>226612</t>
+          <t>210872</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>138523</t>
+          <t>136519</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>192477</t>
+          <t>191386</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>265888</t>
+          <t>263680</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>368978</t>
+          <t>373524</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>51298</t>
+          <t>50861</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>78814</t>
+          <t>77311</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>69896</t>
+          <t>68306</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>105842</t>
+          <t>105084</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>129866</t>
+          <t>128320</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>174260</t>
+          <t>175909</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>28043</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>24743</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>44336</t>
+          <t>44390</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3110_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP3110_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2704</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5787</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6568</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3134</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11549</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10749</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6967</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16278</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6248</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2471</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16915</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16342</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33649</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36187</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29955</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>41918</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>60,05%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>49,71%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>69,56%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>47991</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>38949</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>56122</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>67,21%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>54,55%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>78,6%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42185</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>32930</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49623</t>
+          <t>43516</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>90176</t>
+          <t>74594</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78944</t>
+          <t>66208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101811</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>71,91%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10623</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6443</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16698</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9228</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4189</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19625</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12,92%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12026</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21253</t>
+          <t>16773</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31040</t>
+          <t>24662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1365</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4517</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4346</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4484</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1365</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4400</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1398,57 +1398,57 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5116</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2555</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8787</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6057</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2334</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11787</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10838</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>12250</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19303</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7221</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3646</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13589</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,82%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14184</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5682</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22262</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,72%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14843</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32518</t>
+          <t>29427</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -1741,107 +1741,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>44544</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34294</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56016</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>42967</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18283</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>58539</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>34,2%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>40984</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>31783</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>48542</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>41,26%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>32,0%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>48,87%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>85528</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>71205</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>99840</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>39,91%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>33,23%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>46,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>48162</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>36669</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>61016</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,1%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>48,26%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>91129</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>65202</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>111207</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>36,15%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>25,87%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46010</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36652</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>56131</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>40,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,89%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>48,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>55683</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33606</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>97733</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44,32%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>77,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49867</t>
+          <t>31763</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>42309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>105550</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81466</t>
+          <t>66025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>148015</t>
+          <t>91914</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12060</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5874</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24778</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>5504</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>11396</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29196</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>19205</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35437</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -2080,107 +2080,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1254</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5047</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5935</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1254</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2193,57 +2193,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2971</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2937</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7004</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13320</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8808</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>19336</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>23,25%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>33,75%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>16753</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>11558</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>21911</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>30,16%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>20,81%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>39,44%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>22259</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>31616</t>
+          <t>29963</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24041</t>
+          <t>22543</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39880</t>
+          <t>37142</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>31579</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>25189</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>37534</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>55,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>43,96%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>65,51%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>22969</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>17526</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>28666</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>22374</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>17154</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>27934</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>41,35%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>31,55%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>51,6%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>35809</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>29159</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>42418</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>55,4%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>58778</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49118</t>
+          <t>46090</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67810</t>
+          <t>63134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,67%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>7576</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>12289</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>21,45%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>6403</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>3543</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>20,16%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3502</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>4654</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>9042</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>16,28%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -2875,107 +2875,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1835</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4628</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>4427</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>3058</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1166</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6750</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1457</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>4344</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1242</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>7774</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -2988,57 +2988,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17305</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>12813</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>21486</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>31,02%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>17486</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>12173</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>24854</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>18,5%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>37,77%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21426</t>
+          <t>25223</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>30109</t>
+          <t>30672</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>21744</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40369</t>
+          <t>42226</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>35497</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>22348</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>45875</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>51,26%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>32,27%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>66,24%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>37314</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>30165</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>44603</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>56,7%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>45,84%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>67,78%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36597</t>
+          <t>38350</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>21790</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>47101</t>
+          <t>45004</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>73910</t>
+          <t>73847</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>56864</t>
+          <t>57825</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>87526</t>
+          <t>86379</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,6%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>15960</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5957</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>37096</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>23,05%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>53,57%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>7076</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3728</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>13062</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>19,85%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42152</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54525</t>
+          <t>44424</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -3783,57 +3783,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>69254</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>69254</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>69254</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>65809</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>65809</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>65809</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>73656</t>
+          <t>66573</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>73656</t>
+          <t>66573</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>73656</t>
+          <t>66573</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>139464</t>
+          <t>135826</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>139464</t>
+          <t>135826</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>139464</t>
+          <t>135826</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>2819</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2914</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>8,24%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>2836</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4013,72 +4013,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>4161</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1753</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>7731</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>19,53%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2797</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>6036</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>17,65%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -4126,72 +4126,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>21959</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>17127</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>26785</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>55,48%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>43,27%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>67,67%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>21074</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>16963</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>25089</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>61,62%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>49,6%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>73,36%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26594</t>
+          <t>25893</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>42971</t>
+          <t>43983</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36707</t>
+          <t>37150</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>50220</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>15803</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16286</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>21077</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>26877</t>
+          <t>27489</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -4352,107 +4352,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>4387</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>1747</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>4609</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>418</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -4465,107 +4465,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2549</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2966</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>3284</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>2407</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -4578,57 +4578,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4695,72 +4695,72 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2296</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>5381</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>5162</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>323</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -4808,72 +4808,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12313</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>8178</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>17205</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>26,08%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>36,45%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>11142</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>6928</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>15641</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>15,64%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>35,31%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>14269</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>25411</t>
+          <t>23437</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>18897</t>
+          <t>17589</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>32287</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -4921,72 +4921,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>22602</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>17315</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>28333</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>47,88%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>36,68%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>60,02%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>23829</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>18576</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>28821</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>53,8%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>41,94%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>65,07%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>26112</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>32083</t>
+          <t>29209</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>49942</t>
+          <t>46837</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>41768</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>57318</t>
+          <t>54253</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>59,3%</t>
         </is>
       </c>
     </row>
@@ -5034,72 +5034,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>9997</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>6224</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>15659</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>21,18%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>33,17%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>6544</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>3519</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>10702</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>14,77%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>24,16%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>25014</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -5260,107 +5260,107 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>3866</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4315</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>3727</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -5373,57 +5373,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>27261</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>16152</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>22813</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>37818</t>
+          <t>34606</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>28512</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>49537</t>
+          <t>44346</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -5603,72 +5603,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>34185</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>25998</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>44780</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>24,32%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>18,49%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>31,86%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>38011</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>29831</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>47863</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>30,73%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>38,69%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>34309</t>
+          <t>35817</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>28116</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>45455</t>
+          <t>44345</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>72321</t>
+          <t>70003</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>58388</t>
+          <t>58371</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>86734</t>
+          <t>83320</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -5716,72 +5716,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>61528</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>50689</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>73025</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>43,77%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>36,06%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>51,95%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>49870</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>40701</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>60732</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>40,32%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>32,9%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>49,1%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>68979</t>
+          <t>49804</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>56412</t>
+          <t>41560</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>84524</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>118849</t>
+          <t>111332</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>103880</t>
+          <t>95706</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>136060</t>
+          <t>126619</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -5829,72 +5829,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>19398</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>12224</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>27461</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>13,8%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>19,54%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>14632</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>8985</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>21298</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>17,22%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>34659</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>38009</t>
+          <t>34523</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>27243</t>
+          <t>26275</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>51414</t>
+          <t>45927</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>889</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>818</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -6055,72 +6055,72 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>3563</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2229</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>7666</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>344</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -6168,57 +6168,57 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6285,72 +6285,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>6092</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>1791</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>4718</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>503</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -6398,72 +6398,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>19980</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>12803</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>28090</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>17,88%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>13378</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>8197</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>21369</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>10,4%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>16,61%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>19757</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>28716</t>
+          <t>23792</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>25027</t>
+          <t>25656</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>45073</t>
+          <t>46981</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -6511,72 +6511,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>29012</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>21165</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>39313</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>18,46%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>25,02%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>21833</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>15324</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>30251</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>16,97%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>23,51%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>27867</t>
+          <t>23579</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>16155</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>37452</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>49700</t>
+          <t>52592</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>38990</t>
+          <t>41537</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>61580</t>
+          <t>66156</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -6624,72 +6624,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>26243</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>18929</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>35648</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>12,05%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>22,69%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>32466</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>24966</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>42827</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>25,23%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>33,29%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>35190</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>34573</t>
+          <t>45256</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>58479</t>
+          <t>61433</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>47169</t>
+          <t>48549</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>70410</t>
+          <t>73777</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -6737,72 +6737,72 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>67125</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>55163</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>78269</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>42,72%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>35,11%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>49,81%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>50465</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>41411</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>60935</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>32,19%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>47,36%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>65659</t>
+          <t>53354</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>55012</t>
+          <t>43166</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>75930</t>
+          <t>63990</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>116123</t>
+          <t>120479</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>101672</t>
+          <t>105702</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>129823</t>
+          <t>135484</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -6850,72 +6850,72 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13351</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>7913</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>20811</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>8733</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>5015</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>13979</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>13977</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>22101</t>
+          <t>21961</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>31988</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -6963,57 +6963,57 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7080,72 +7080,72 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>37952</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>29225</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>50485</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>40373</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>30128</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>51529</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>45033</t>
+          <t>37756</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>34591</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>59053</t>
+          <t>47372</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7155,32 +7155,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>85406</t>
+          <t>75708</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>71348</t>
+          <t>63309</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>103231</t>
+          <t>91287</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -7193,72 +7193,72 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>114742</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>96436</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>133940</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>16,72%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>19,52%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>119999</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>100603</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>139248</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>18,48%</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>21,45%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>125847</t>
+          <t>116854</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>107952</t>
+          <t>102054</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>147416</t>
+          <t>133577</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7268,32 +7268,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>245846</t>
+          <t>231596</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>219720</t>
+          <t>208301</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>273279</t>
+          <t>256635</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -7306,72 +7306,72 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>282909</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>257184</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>307842</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>41,22%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>44,86%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>385</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>267846</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>231260</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>293671</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>41,25%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>35,62%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>45,23%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>307608</t>
+          <t>259757</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>278181</t>
+          <t>239151</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>336364</t>
+          <t>280857</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7381,32 +7381,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>575455</t>
+          <t>542665</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>531070</t>
+          <t>510163</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>619216</t>
+          <t>575200</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,23%</t>
         </is>
       </c>
     </row>
@@ -7419,72 +7419,72 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>146995</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>126823</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>174502</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>18,48%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>25,43%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>141807</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>112716</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>210872</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>160247</t>
+          <t>117630</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>136519</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>191386</t>
+          <t>135713</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>302054</t>
+          <t>264625</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>263680</t>
+          <t>237938</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>373524</t>
+          <t>294409</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -7532,72 +7532,72 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>84926</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>69817</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>105762</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>64416</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>50861</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>77311</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>67493</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>68306</t>
+          <t>55059</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>105084</t>
+          <t>81345</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>149624</t>
+          <t>152419</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>128320</t>
+          <t>130850</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>175909</t>
+          <t>175887</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -7645,72 +7645,72 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>18739</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>27125</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>14818</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>9258</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>21321</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>21631</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,32 +7720,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>25101</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>44390</t>
+          <t>45523</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -7758,57 +7758,57 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>649260</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>649260</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>649260</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>743022</t>
+          <t>614318</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>743022</t>
+          <t>614318</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>743022</t>
+          <t>614318</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>1392282</t>
+          <t>1300580</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>1392282</t>
+          <t>1300580</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>1392282</t>
+          <t>1300580</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
